--- a/output/laminas_comunales/comunal_s_isapre_a_2023_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2023_valparaiso.xlsx
@@ -375,301 +375,301 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Concón</t>
         </is>
       </c>
       <c r="C2">
-        <v>58570</v>
+        <v>31.07813501877805</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="C3">
-        <v>27109</v>
+        <v>21.1308217890052</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quilpué</t>
+          <t>Zapallar</t>
         </is>
       </c>
       <c r="C4">
-        <v>20521</v>
+        <v>18.42848037876719</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Concón</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="C5">
-        <v>16964</v>
+        <v>17.10565698892547</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
+          <t>Viña del Mar</t>
         </is>
       </c>
       <c r="C6">
-        <v>14572</v>
+        <v>16.89434759031279</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Rinconada</t>
         </is>
       </c>
       <c r="C7">
-        <v>8927</v>
+        <v>15.79855663633511</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="C8">
-        <v>8891</v>
+        <v>15.75697116526531</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="C9">
-        <v>6665</v>
+        <v>12.72486244547709</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Quilpué</t>
         </is>
       </c>
       <c r="C10">
-        <v>6047</v>
+        <v>12.03217805817615</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>San Esteban</t>
         </is>
       </c>
       <c r="C11">
-        <v>4820</v>
+        <v>11.57805269619416</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Calle Larga</t>
         </is>
       </c>
       <c r="C12">
-        <v>4572</v>
+        <v>10.71240414447111</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>Villa Alemana</t>
         </is>
       </c>
       <c r="C13">
-        <v>3371</v>
+        <v>10.67522325516655</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="C14">
-        <v>3317</v>
+        <v>9.475236573675803</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="C15">
-        <v>3133</v>
+        <v>8.867403314917127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Olmué</t>
         </is>
       </c>
       <c r="C16">
-        <v>2698</v>
+        <v>8.787296828891282</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>San Esteban</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="C17">
-        <v>2452</v>
+        <v>8.782746175428139</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="C18">
-        <v>2247</v>
+        <v>8.774388378450395</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="C19">
-        <v>2128</v>
+        <v>8.469066821288633</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zapallar</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="C20">
-        <v>2024</v>
+        <v>8.419553357878046</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rinconada</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="C21">
-        <v>2014</v>
+        <v>8.274296930107033</v>
       </c>
     </row>
     <row r="22">
@@ -684,67 +684,67 @@
         </is>
       </c>
       <c r="C22">
-        <v>1981</v>
+        <v>8.181893276061457</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Olmué</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="C23">
-        <v>1876</v>
+        <v>8.00533288492259</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
+          <t>El Quisco</t>
         </is>
       </c>
       <c r="C24">
-        <v>1830</v>
+        <v>7.141564083997103</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>El Tabo</t>
         </is>
       </c>
       <c r="C25">
-        <v>1578</v>
+        <v>6.836125553629886</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>El Tabo</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="C26">
-        <v>1420</v>
+        <v>5.890145427271753</v>
       </c>
     </row>
     <row r="27">
@@ -759,112 +759,112 @@
         </is>
       </c>
       <c r="C27">
-        <v>1265</v>
+        <v>5.573669369051816</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="C28">
-        <v>1163</v>
+        <v>5.550745550745551</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="C29">
-        <v>906</v>
+        <v>5.219693909609084</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="C30">
-        <v>843</v>
+        <v>5.082033768777016</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>Santa María</t>
         </is>
       </c>
       <c r="C31">
-        <v>771</v>
+        <v>4.703000612369872</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Santa María</t>
+          <t>Catemu</t>
         </is>
       </c>
       <c r="C32">
-        <v>768</v>
+        <v>4.663113818043396</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Catemu</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="C33">
-        <v>735</v>
+        <v>4.434041657900273</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="C34">
-        <v>577</v>
+        <v>3.296943231441048</v>
       </c>
     </row>
     <row r="35">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>297</v>
+        <v>2.873452012383901</v>
       </c>
     </row>
     <row r="36">
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>238</v>
+        <v>2.773569514042652</v>
       </c>
     </row>
     <row r="37">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>0.8055235903337169</v>
       </c>
     </row>
   </sheetData>
@@ -965,7 +965,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
